--- a/Översikt HÄSSLEHOLM.xlsx
+++ b/Översikt HÄSSLEHOLM.xlsx
@@ -566,7 +566,7 @@
         <v>45427</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>45427</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>45427</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>46174</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>44378</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45427</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45392</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45348</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>46149</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>44454</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44952</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>46168</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45687</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45687</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45391</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45708</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>45194</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45708</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45014</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45812</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45687</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44434</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45463</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44897</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45014</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45583</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>46149</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>45708</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44862</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44584</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>44659</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44648</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44896</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45105</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45687</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44910</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45150</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45021</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45378</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45266</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45385</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45714</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45750</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45751</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45708</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>44741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45062</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45896</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45774</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45648</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45341</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45645</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45673</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45566</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45799</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45751</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>45958</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>45617</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>45455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>45817</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45463</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45141</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45980</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>45825</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>46013</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44565</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>45810</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46098</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>46181</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44883</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44454</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44470</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44886</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>44886</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44797</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44742</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44454</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44501</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44389</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44560</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44564</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>44406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44799</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44454</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44470</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44652</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44606</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44558</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44722</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44456</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44480</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44488</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44480</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44439</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44609</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44587</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44887</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44879</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44459</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44531</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44735</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44820</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44438</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44438</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44497</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44580</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44806</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44497</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44796</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>44806</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44887</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44584</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44616</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44425</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44382</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44558</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44846</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44435</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44844</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44659</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44433</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44466</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44509</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>44595</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44397</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>44379</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44582</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44378</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44382</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>44588</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44420</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44511</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44580</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44482</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44461</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44565</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44375</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>44817</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44446</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44480</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44466</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44558</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44463</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44530</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44495</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44664</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44467</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44462</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>44732</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44551</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44581</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44744</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>44564</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>44599</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45558</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45558</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44593</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45595</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44882</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44875</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44600</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44949</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44844</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45516</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44944</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44565</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44914</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44918</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44964</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45321</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44434</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44937</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45540</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45540</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45462</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44949</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45313</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>45314</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44953</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>44955</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44462</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45321</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45548</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44512</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44887</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45210</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44959</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45393</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45231</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45054</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44985</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45061</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44607</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44729</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45750</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45071</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44760</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44378</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45626</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45210</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44792</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44480</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44967</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45510</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44978</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44587</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>44992</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44734</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>44847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44844</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44700</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45600</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44914</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45603</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44481</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45617</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45008</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45626</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45435</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45576</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45055</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44441</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45702</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45702</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45561</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44634</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45092</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44806</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45550</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45029</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44775</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>44533</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45329</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>44981</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45098</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45327</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45014</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45329</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45687</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>44475</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45043</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45259</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44746</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45321</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44525</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45576</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45774</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45688</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>44981</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>44981</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45636</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45370</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45001</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45370</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44971</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45335</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44915</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45300</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45145</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45564</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45401</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>44638</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45043</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45414</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45215</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45418</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45210</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45210</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>44714</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45057</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44607</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45714</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45125</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44895</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44830</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45078</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44606</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44659</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45620</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45057</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>44858</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>44462</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45154</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45560</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45588</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45356</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44942</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45732</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45702</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44743</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>44937</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45734</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44441</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>44915</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45119</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44967</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45356</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45356</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44953</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44833</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44937</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45399</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45510</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>44615</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45462</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45142</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45142</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45702</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45235</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44379</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45585</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45000</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45006</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45250</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45209</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45435</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>44895</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>44438</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44873</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45302</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45062</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45471</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44831</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45447</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44811</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45604</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45365</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44915</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45107</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44379</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45325</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45204</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44428</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45191</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45735</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45384</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45142</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45477</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45015</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45447</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>44474</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44873</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44952</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45462</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44946</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44946</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45751</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45754</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45086</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44984</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44868</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45469</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45469</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45310</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45461</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45387</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45005</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45063</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45005</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44959</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45124</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45462</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>44746</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44998</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45001</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45363</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44875</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44915</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45799</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45742</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45716</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45253</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45323</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>44915</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44922</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>44914</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45190</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45715</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45636</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45714</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>44897</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>44897</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45602</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44883</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44452</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45231</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44964</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>44860</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45099</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45320</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45323</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45026</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45594</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45510</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44573</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45369</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45147</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45889</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45593</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45079</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45456</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45204</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45727</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45051</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45636</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45210</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45077</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44984</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45444</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44881</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45092</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45246</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45145</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45190</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45294</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45044</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45245</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44583</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45086</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44958</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45503</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44986</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45096</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>44957</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>44957</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44449</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44967</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45511</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45254</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45254</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45516</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45463</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45595</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45455</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45636</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44739</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44881</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44463</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44999</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45593</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44877</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45176</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45217</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44466</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45485</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45644</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45601</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44405</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>44918</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44900</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45567</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44986</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44986</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45891</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45519</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45058</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45901</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>45119</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45050</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45901</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45174</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45645</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45736</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45148</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45629</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45632</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45217</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45905</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45910</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45040</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45700</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>44531</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45635</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45224</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45911</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44403</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45912</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45912</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45734</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44719</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44719</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45912</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45219</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>46182</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45243</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45476</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45341</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45715</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45695</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45702</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45224</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>46182</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45313</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45471</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45212</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45917</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45917</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45917</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45922</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45708</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45922</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45919</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45922</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45716</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45923</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44859</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45702</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45777</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44986</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45779</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45923</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>45923</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44986</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44972</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45923</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45440</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45716</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45485</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45772</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45646</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45646</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46055</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45349</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45727</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45164</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45644</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45660</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45247</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45645</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45051</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45670</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45784</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45023</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45105</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45322</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44448</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45266</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45386</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45702</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>44844</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45614</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45929</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45720</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45051</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45209</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44883</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>44881</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45485</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45555</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>44916</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45243</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45803</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45313</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45504</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45600</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45737</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45717</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45537</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>44375</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45385</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45790</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45008</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45701</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>44553</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45474</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45628</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45675</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>46050</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45933</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>44951</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45712</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45789</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45524</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45015</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>44470</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45935</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45755</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>46183</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45008</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45218</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45554</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45503</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45475</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>44810</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45541</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45190</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45399</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45411</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45735</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45938</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45726</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45331</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>44946</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45624</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45644</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45254</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44820</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45796</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46182</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45940</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45930</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44882</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45796</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>44425</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>44910</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45706</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45692</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>44977</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45796</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>44454</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45644</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>44441</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45799</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45946</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>44915</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45511</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>44452</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>46182</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45945</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45721</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>45671</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>44881</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45747</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45513</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45754</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45622</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45597</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45077</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45692</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45798</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44593</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>46182</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45797</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>46162</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45947</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45516</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>46182</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45202</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45475</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>44812</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45484</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>44802</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44573</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>45947</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45294</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>44638</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45799</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>45715</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>45951</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45222</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>46183</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>45800</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>45726</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>44940</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45803</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45008</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>44917</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45800</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45800</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45726</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45335</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45749</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45726</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45930</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45805</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>44910</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45105</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45092</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45805</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45957</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45233</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45092</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45545</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45058</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45595</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45702</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45702</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45016</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>44518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45063</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45558</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45959</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45282</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45119</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45350</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45119</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45356</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45751</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44915</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44501</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45086</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>44490</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45812</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>45929</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45217</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45016</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45817</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45015</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45396,7 +45396,7 @@
         <v>45147</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>44847</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45353</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45817</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45817</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44859</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45817</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45966</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45930</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45817</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45736</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45968</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45478</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45971</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45971</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45821</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46365,7 +46365,7 @@
         <v>45362</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>45971</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45821</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45532</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45519</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45087</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>45471</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45302</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45589</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>44873</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45427</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>44872</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45084</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45447</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45109</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45832</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45303</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44992</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45463</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45306</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45510</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45485</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45978</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45348</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>46132</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45975</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45978</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>44999</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45398</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45314</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45153</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45978</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45838</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45838</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>46188</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>46188</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45826</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45826</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45971</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45084</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>46188</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45930</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45020</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45842</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45981</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>45930</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45842</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45723</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>45624</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45842</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45139</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45844</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45985</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45727</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>44971</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45844</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45265</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45125</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>44565</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>44467</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45503</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45517</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45849</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45161</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45670</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45777</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>44599</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45757</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>44992</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>44583</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45698</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45355</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45445</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45009</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45770</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>46148</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>44999</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>45867</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50997,7 +50997,7 @@
         <v>45114</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45191</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45547</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45630</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51225,7 +51225,7 @@
         <v>45645</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>44650</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45086</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45156</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45168</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45708</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>45148</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>46006</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45328</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>45078</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45727</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>45589</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45876</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>46010</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>45876</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>46010</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52194,7 +52194,7 @@
         <v>45812</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45079</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45079</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45218</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45839</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45761</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>46013</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45351</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46013</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>45569</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>44812</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>45044</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45646</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45348</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>46149</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>46149</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>46149</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>46135</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45617</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45665</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46030</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45117</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>46149</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45132</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45132</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>46149</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45124</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>46034</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44714</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45148</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45148</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>44802</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>46034</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>44728</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>46034</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45702</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54313,7 +54313,7 @@
         <v>46174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>46034</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>46034</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>46192</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54541,7 +54541,7 @@
         <v>46149</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54598,7 +54598,7 @@
         <v>46035</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45621</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>44671</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>44671</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46035</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45254</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45237</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45446</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45198</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>46041</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45254</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>46043</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>46043</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45715</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>46043</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45222</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45096</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45209</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45208</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>46049</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45756</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45205</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45722</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44882</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45322</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>46049</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>46049</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>46050</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56261,7 +56261,7 @@
         <v>45233</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56318,7 +56318,7 @@
         <v>45247</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>45252</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45314</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>46051</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45294</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45708</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45109</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>46055</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46055</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45180</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45265</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>46055</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>46055</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>46057</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45266</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>46058</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45322</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45322</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>44974</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45320</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45237</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45302</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45715</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45726</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>46059</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45245</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>46064</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>46064</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>46066</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>44959</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>44959</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>46066</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45503</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45986</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>44480</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>45266</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>44826</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58660,7 +58660,7 @@
         <v>45044</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58717,7 +58717,7 @@
         <v>45235</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45180</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>45511</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45755</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45040</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45742</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>44883</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45077</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45078</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>46073</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45455</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45299</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>45973</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>44882</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>44970</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45726</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45215</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45485</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45246</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>46013</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>44830</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45978</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45978</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45547</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45463</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>44475</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>46085</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60266,7 +60266,7 @@
         <v>46085</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45646</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>45470</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>44900</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>45679</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60551,7 +60551,7 @@
         <v>45391</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>46093</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>44805</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>44565</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>46093</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>44949</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45184</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>44897</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>44974</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>44599</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>44967</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>46095</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>46093</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>44606</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>46099</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>46098</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>46098</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>46098</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>46098</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>46100</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46100</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>46100</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>46100</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>46100</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>46104</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>46104</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>46107</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>46107</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>46108</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>46112</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>46112</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>46161</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46121</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62447,7 +62447,7 @@
         <v>46121</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>46162</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>46162</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45510</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>46162</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62732,7 +62732,7 @@
         <v>46162</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62789,7 +62789,7 @@
         <v>46162</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>46162</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46162</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62960,7 +62960,7 @@
         <v>46162</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63017,7 +63017,7 @@
         <v>46162</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>46162</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63131,7 +63131,7 @@
         <v>46124</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>46126</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>46168</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>46126</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>46127</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63416,7 +63416,7 @@
         <v>46104</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>46174</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>46007</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>46132</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>46129</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63701,7 +63701,7 @@
         <v>46134</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63758,7 +63758,7 @@
         <v>46133</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63815,7 +63815,7 @@
         <v>46175</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>46175</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>46175</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>46175</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64043,7 +64043,7 @@
         <v>46176</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45670</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>45798</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>45966</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>46177</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64328,7 +64328,7 @@
         <v>45777</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64385,7 +64385,7 @@
         <v>45736</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64442,7 +64442,7 @@
         <v>44396</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>46176</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64556,7 +64556,7 @@
         <v>46176</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>44937</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>45789</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>45697</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>44607</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>44722</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -64908,7 +64908,7 @@
         <v>44405</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -64965,7 +64965,7 @@
         <v>46181</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>46177</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65079,7 +65079,7 @@
         <v>45735</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>45266</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65193,7 +65193,7 @@
         <v>45260</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>45192</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65307,7 +65307,7 @@
         <v>46181</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>46139</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>45735</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>45842</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>46182</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>46181</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65654,7 +65654,7 @@
         <v>45715</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>46139</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>

--- a/Översikt HÄSSLEHOLM.xlsx
+++ b/Översikt HÄSSLEHOLM.xlsx
@@ -566,7 +566,7 @@
         <v>45427</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>45427</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>45427</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>46174</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>44378</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45427</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45392</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>45348</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>46149</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>44454</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>44952</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>46168</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45687</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45687</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45391</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45708</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>45194</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45708</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45014</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45812</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>45687</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>44434</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>45463</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>44897</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45014</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>45583</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>46149</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>45708</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44862</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44584</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>44659</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44648</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44896</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>45105</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45687</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>44910</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45150</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45021</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45378</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>44838</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>45266</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>45385</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>45714</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>45750</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>45751</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>45708</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>44741</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>45062</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45896</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         <v>45774</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45648</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>45341</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
         <v>45645</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45673</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>45566</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45799</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>45751</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>45958</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>45617</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>45455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
         <v>45817</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45463</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45141</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>45980</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>45825</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>46013</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44565</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>45810</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>46098</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>46181</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         <v>44883</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44454</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44470</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>44438</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44886</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
         <v>44886</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         <v>44797</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>44742</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>44454</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>44501</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44389</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44560</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>44564</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>44406</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44799</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44454</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44470</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44652</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44606</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44558</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44722</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44376</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44456</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44480</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>44488</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44480</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>44439</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>44609</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44587</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44887</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>44879</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44459</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>44531</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>44735</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>44820</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44438</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>44438</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>44497</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44580</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44806</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9320,7 +9320,7 @@
         <v>44497</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44796</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>44806</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44887</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44584</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44616</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44588</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44425</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44382</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44558</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         <v>44846</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>44435</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44844</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>44659</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>44433</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44466</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>44509</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>44595</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44397</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10428,7 +10428,7 @@
         <v>44379</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44375</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44582</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>44378</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>44382</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>44588</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>44420</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>44573</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
         <v>44511</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44580</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44482</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44461</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44565</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44375</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>44817</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>44446</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44480</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11417,7 +11417,7 @@
         <v>44600</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>44466</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44558</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44463</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44530</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44495</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>44664</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44467</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44462</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>44735</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
         <v>44732</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>44551</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>44581</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44744</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>44564</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
         <v>44599</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>45558</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>45558</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44593</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45595</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12629,7 +12629,7 @@
         <v>44882</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44875</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44600</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44949</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44844</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45516</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44944</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13043,7 +13043,7 @@
         <v>44565</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>44914</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>44918</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44964</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45321</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44606</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44434</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44937</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45540</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45540</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45462</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44949</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45313</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>45314</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>44953</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>44955</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>44462</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14022,7 +14022,7 @@
         <v>45321</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45548</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44512</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44887</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45210</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44959</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45393</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45231</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45054</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>44985</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45061</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>44607</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14711,7 +14711,7 @@
         <v>44729</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14768,7 +14768,7 @@
         <v>45750</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>45071</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>44760</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44378</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45626</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45210</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44792</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15167,7 +15167,7 @@
         <v>44480</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44967</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45510</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44978</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44587</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>44992</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44734</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>44847</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44844</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>44700</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45600</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44914</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44914</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>45603</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44481</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45617</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45008</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45626</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>45435</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45576</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45055</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44441</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45702</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45702</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45561</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44634</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45092</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44806</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45550</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45029</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44775</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>44533</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45329</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>44981</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45098</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45327</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45014</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44950</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45329</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45687</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>44475</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45043</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45259</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>44746</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45321</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44525</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45576</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         <v>45774</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>45688</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>44981</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>44981</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45636</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45370</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45001</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45370</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>44971</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45335</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>44915</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45300</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45145</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45564</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45401</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>44638</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45043</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45414</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45215</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45418</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>45418</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19254,7 +19254,7 @@
         <v>45210</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45210</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>44714</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45057</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>44607</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45714</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45125</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44895</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19715,7 +19715,7 @@
         <v>45125</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19772,7 +19772,7 @@
         <v>44830</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45078</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19886,7 +19886,7 @@
         <v>44606</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         <v>44659</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45620</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45057</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>44858</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>44462</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45154</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45560</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45588</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>45356</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44942</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45732</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20590,7 +20590,7 @@
         <v>45702</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44743</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>44937</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45734</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>44441</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>44915</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45119</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>44967</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45356</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45356</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44953</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44833</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44937</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45399</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45510</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>44615</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45462</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45142</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45142</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45702</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45235</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>44379</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45585</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45000</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45006</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45250</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>45209</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>45435</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>44895</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>44438</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22362,7 +22362,7 @@
         <v>44873</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45302</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         <v>45062</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45471</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22590,7 +22590,7 @@
         <v>44831</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45447</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22704,7 +22704,7 @@
         <v>44811</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
         <v>45604</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45365</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>44915</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45107</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44379</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>45325</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45204</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23160,7 +23160,7 @@
         <v>44428</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23217,7 +23217,7 @@
         <v>45191</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45735</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>45384</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23388,7 +23388,7 @@
         <v>45142</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23445,7 +23445,7 @@
         <v>45477</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>45015</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45447</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>44474</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>44873</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23730,7 +23730,7 @@
         <v>44952</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45462</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44946</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>44946</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45751</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45754</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45086</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44984</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44868</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45469</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45469</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>45310</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45461</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45387</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45005</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45063</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>44515</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45005</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>44959</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45124</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45462</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>44746</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44998</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45001</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45363</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>44875</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44915</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45799</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45379</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45742</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45716</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45253</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45323</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>44915</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25678,7 +25678,7 @@
         <v>44922</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>44914</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45190</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45715</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45636</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45714</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>44897</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>44897</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45602</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>44883</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>44452</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45231</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>44964</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>44860</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45099</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45320</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         <v>45323</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45026</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45594</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45510</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26818,7 +26818,7 @@
         <v>44573</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26875,7 +26875,7 @@
         <v>45369</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>45147</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45889</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>45593</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45079</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45456</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45204</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27274,7 +27274,7 @@
         <v>45727</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27331,7 +27331,7 @@
         <v>45051</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27388,7 +27388,7 @@
         <v>45636</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45210</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45077</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>44984</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45444</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44881</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45092</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>45246</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45145</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45190</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45294</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45044</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45245</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>44583</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45086</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>44958</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45503</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44986</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45096</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>44957</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>44957</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>44449</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>44967</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45511</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28813,7 +28813,7 @@
         <v>45254</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45254</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45516</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45463</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45595</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>45455</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45636</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>44739</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45407</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>44881</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>44463</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44999</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>45889</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45593</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44877</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45176</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45217</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>44466</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45485</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45644</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>44742</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45601</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>44405</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>44918</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30181,7 +30181,7 @@
         <v>44900</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>45567</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>44986</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44986</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45891</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45519</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45058</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45901</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30647,7 +30647,7 @@
         <v>45119</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>45050</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45901</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45174</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45645</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45736</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>45148</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45629</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         <v>45632</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31165,7 +31165,7 @@
         <v>45217</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31222,7 +31222,7 @@
         <v>45905</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45910</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45040</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45700</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31450,7 +31450,7 @@
         <v>44531</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31507,7 +31507,7 @@
         <v>45635</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45224</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45911</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>44403</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>45912</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>45912</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45734</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44719</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44719</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32092,7 +32092,7 @@
         <v>45912</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32149,7 +32149,7 @@
         <v>45219</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>46182</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45243</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32325,7 +32325,7 @@
         <v>45476</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32382,7 +32382,7 @@
         <v>45341</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45715</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45695</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>45702</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>45224</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>45594</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>46182</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32786,7 +32786,7 @@
         <v>45313</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32843,7 +32843,7 @@
         <v>45471</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32900,7 +32900,7 @@
         <v>44820</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32957,7 +32957,7 @@
         <v>45212</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>45917</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33071,7 +33071,7 @@
         <v>45917</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45917</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33185,7 +33185,7 @@
         <v>45922</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33242,7 +33242,7 @@
         <v>45708</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>45922</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>45919</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33413,7 +33413,7 @@
         <v>45922</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33470,7 +33470,7 @@
         <v>45716</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33527,7 +33527,7 @@
         <v>45923</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44859</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45702</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>45777</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>44986</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45779</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45923</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>45923</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44986</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>44972</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45923</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45440</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45716</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45485</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45772</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45646</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45646</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>46055</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45349</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45727</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34734,7 +34734,7 @@
         <v>45164</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34791,7 +34791,7 @@
         <v>45926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>45644</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45660</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45247</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45645</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45051</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45670</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45784</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45023</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45105</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45322</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>44448</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45266</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35532,7 +35532,7 @@
         <v>45386</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45702</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>44844</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45614</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45929</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45720</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45051</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45209</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45693</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>44883</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>44881</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45485</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45555</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>44916</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45243</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45803</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45313</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45504</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45600</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45737</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45717</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>45537</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>44375</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45385</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45790</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45008</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45701</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>44553</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45474</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45628</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45675</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>46050</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45933</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37485,7 +37485,7 @@
         <v>45790</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>44951</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45712</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45789</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45524</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45015</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>44470</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45935</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45755</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>46183</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45008</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45218</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38169,7 +38169,7 @@
         <v>45554</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>45503</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45475</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>44810</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45541</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45190</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45399</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45411</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>45735</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45938</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45726</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>45331</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>44946</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45624</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45644</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45254</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44820</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>45796</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>46182</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45940</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45930</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44882</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45796</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>44425</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>44910</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39619,7 +39619,7 @@
         <v>45706</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45692</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>44977</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45796</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>44454</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45644</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>44441</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>45799</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>45946</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>44915</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45511</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>44452</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>46182</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45945</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45721</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>45671</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40593,7 +40593,7 @@
         <v>44881</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45747</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45513</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45754</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40821,7 +40821,7 @@
         <v>45622</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40878,7 +40878,7 @@
         <v>45597</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40935,7 +40935,7 @@
         <v>45077</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45692</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>45965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45798</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41163,7 +41163,7 @@
         <v>44593</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         <v>46182</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41277,7 +41277,7 @@
         <v>45797</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41334,7 +41334,7 @@
         <v>46162</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41391,7 +41391,7 @@
         <v>45947</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41448,7 +41448,7 @@
         <v>45516</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41505,7 +41505,7 @@
         <v>46182</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>45202</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45475</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>44812</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41738,7 +41738,7 @@
         <v>45484</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>44802</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41852,7 +41852,7 @@
         <v>44573</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>45947</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41971,7 +41971,7 @@
         <v>45294</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>44638</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45799</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>45715</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45078</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>45078</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42313,7 +42313,7 @@
         <v>45951</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42370,7 +42370,7 @@
         <v>45222</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>46183</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42484,7 +42484,7 @@
         <v>45800</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>45726</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42598,7 +42598,7 @@
         <v>44940</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>45803</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42712,7 +42712,7 @@
         <v>45008</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>44917</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45800</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42883,7 +42883,7 @@
         <v>45800</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42940,7 +42940,7 @@
         <v>45726</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42997,7 +42997,7 @@
         <v>45335</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>45749</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45726</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>45930</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>45805</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43282,7 +43282,7 @@
         <v>44910</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43344,7 +43344,7 @@
         <v>45105</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>45092</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43458,7 +43458,7 @@
         <v>45805</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45957</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45233</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45092</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43686,7 +43686,7 @@
         <v>45545</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43743,7 +43743,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>45058</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43857,7 +43857,7 @@
         <v>45595</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45702</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45702</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45016</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44085,7 +44085,7 @@
         <v>44518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44142,7 +44142,7 @@
         <v>45063</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44199,7 +44199,7 @@
         <v>45063</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44256,7 +44256,7 @@
         <v>45558</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45959</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44370,7 +44370,7 @@
         <v>45282</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>45065</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45119</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>45350</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45119</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44655,7 +44655,7 @@
         <v>45356</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45751</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44769,7 +44769,7 @@
         <v>44915</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44915</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>44501</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>45086</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44997,7 +44997,7 @@
         <v>44490</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45054,7 +45054,7 @@
         <v>45812</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45111,7 +45111,7 @@
         <v>45929</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45168,7 +45168,7 @@
         <v>45217</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45016</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45817</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>45015</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45396,7 +45396,7 @@
         <v>45147</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45453,7 +45453,7 @@
         <v>44847</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45510,7 +45510,7 @@
         <v>45353</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45567,7 +45567,7 @@
         <v>45817</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45624,7 +45624,7 @@
         <v>45817</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>44859</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>45817</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>45966</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>45930</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>45817</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45966,7 +45966,7 @@
         <v>45736</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46023,7 +46023,7 @@
         <v>45968</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45096</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45478</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>45971</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45971</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45821</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46365,7 +46365,7 @@
         <v>45362</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>45971</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46479,7 +46479,7 @@
         <v>45821</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>45532</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>45519</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45087</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>45471</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46764,7 +46764,7 @@
         <v>45302</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46821,7 +46821,7 @@
         <v>45589</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46878,7 +46878,7 @@
         <v>44873</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45427</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>44872</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47049,7 +47049,7 @@
         <v>45084</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47106,7 +47106,7 @@
         <v>45447</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47163,7 +47163,7 @@
         <v>45109</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47220,7 +47220,7 @@
         <v>45832</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>45303</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47334,7 +47334,7 @@
         <v>44992</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45463</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45306</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47510,7 +47510,7 @@
         <v>45510</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45485</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45978</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47681,7 +47681,7 @@
         <v>45348</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>46132</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47795,7 +47795,7 @@
         <v>45975</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47852,7 +47852,7 @@
         <v>45978</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47909,7 +47909,7 @@
         <v>44999</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47966,7 +47966,7 @@
         <v>45398</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48023,7 +48023,7 @@
         <v>45314</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45153</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>45978</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48199,7 +48199,7 @@
         <v>45838</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45838</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48313,7 +48313,7 @@
         <v>44974</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         <v>44974</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>46188</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48484,7 +48484,7 @@
         <v>46188</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48541,7 +48541,7 @@
         <v>45826</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48598,7 +48598,7 @@
         <v>45826</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48655,7 +48655,7 @@
         <v>45971</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48712,7 +48712,7 @@
         <v>45084</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48769,7 +48769,7 @@
         <v>46188</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45930</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45020</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>45842</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45138</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45981</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>45930</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49168,7 +49168,7 @@
         <v>45842</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49225,7 +49225,7 @@
         <v>45723</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>45624</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45842</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45139</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45844</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45985</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45727</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>44971</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45844</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45265</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45125</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49857,7 +49857,7 @@
         <v>44565</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49914,7 +49914,7 @@
         <v>44467</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49971,7 +49971,7 @@
         <v>45503</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -50028,7 +50028,7 @@
         <v>45517</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50085,7 +50085,7 @@
         <v>45849</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>45161</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45670</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>45777</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>44599</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50370,7 +50370,7 @@
         <v>45757</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>44992</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>44583</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50541,7 +50541,7 @@
         <v>45698</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50598,7 +50598,7 @@
         <v>45355</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50655,7 +50655,7 @@
         <v>45445</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45009</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45770</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>46148</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>44999</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>45867</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50997,7 +50997,7 @@
         <v>45114</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51054,7 +51054,7 @@
         <v>45191</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45547</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51168,7 +51168,7 @@
         <v>45630</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51225,7 +51225,7 @@
         <v>45645</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51282,7 +51282,7 @@
         <v>44650</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51339,7 +51339,7 @@
         <v>45086</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51396,7 +51396,7 @@
         <v>45156</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45168</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>45708</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>45148</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51624,7 +51624,7 @@
         <v>45148</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>46006</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>45328</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>45078</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45727</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>45589</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>45876</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>46010</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>45876</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>46010</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52194,7 +52194,7 @@
         <v>45812</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52251,7 +52251,7 @@
         <v>45079</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>45079</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52365,7 +52365,7 @@
         <v>45218</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52422,7 +52422,7 @@
         <v>45839</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>45761</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>46013</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45351</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>46013</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>45569</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52769,7 +52769,7 @@
         <v>45055</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52826,7 +52826,7 @@
         <v>44812</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52883,7 +52883,7 @@
         <v>45044</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52940,7 +52940,7 @@
         <v>45646</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52997,7 +52997,7 @@
         <v>45348</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53054,7 +53054,7 @@
         <v>46149</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53111,7 +53111,7 @@
         <v>46149</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>46149</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53225,7 +53225,7 @@
         <v>46135</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45617</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>45665</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>46030</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53458,7 +53458,7 @@
         <v>45117</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53515,7 +53515,7 @@
         <v>46149</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         <v>45132</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53629,7 +53629,7 @@
         <v>45132</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53686,7 +53686,7 @@
         <v>46149</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53743,7 +53743,7 @@
         <v>45124</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53800,7 +53800,7 @@
         <v>46034</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44714</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53914,7 +53914,7 @@
         <v>45148</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53971,7 +53971,7 @@
         <v>45148</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>44802</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>46034</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>44728</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54199,7 +54199,7 @@
         <v>46034</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45702</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54313,7 +54313,7 @@
         <v>46174</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>46034</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>46034</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>46192</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54541,7 +54541,7 @@
         <v>46149</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54598,7 +54598,7 @@
         <v>46035</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45621</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54717,7 +54717,7 @@
         <v>44671</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54774,7 +54774,7 @@
         <v>44671</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54831,7 +54831,7 @@
         <v>46035</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54893,7 +54893,7 @@
         <v>45254</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45237</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45446</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45198</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45198</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>46041</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55235,7 +55235,7 @@
         <v>45254</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>46043</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55349,7 +55349,7 @@
         <v>46043</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55406,7 +55406,7 @@
         <v>45715</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55463,7 +55463,7 @@
         <v>46043</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>45222</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>45096</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55634,7 +55634,7 @@
         <v>45209</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55691,7 +55691,7 @@
         <v>45208</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55748,7 +55748,7 @@
         <v>46049</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55805,7 +55805,7 @@
         <v>45756</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55862,7 +55862,7 @@
         <v>45205</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>45722</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55976,7 +55976,7 @@
         <v>44882</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56033,7 +56033,7 @@
         <v>45322</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>46049</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56147,7 +56147,7 @@
         <v>46049</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56204,7 +56204,7 @@
         <v>46050</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56261,7 +56261,7 @@
         <v>45233</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56318,7 +56318,7 @@
         <v>45247</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56375,7 +56375,7 @@
         <v>45252</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56432,7 +56432,7 @@
         <v>45314</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56489,7 +56489,7 @@
         <v>46051</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56546,7 +56546,7 @@
         <v>45294</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56603,7 +56603,7 @@
         <v>45708</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56660,7 +56660,7 @@
         <v>45109</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56717,7 +56717,7 @@
         <v>46055</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46055</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45180</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>45265</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56945,7 +56945,7 @@
         <v>46055</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -57002,7 +57002,7 @@
         <v>46055</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>45313</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>46057</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45266</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57230,7 +57230,7 @@
         <v>46058</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57287,7 +57287,7 @@
         <v>45322</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57344,7 +57344,7 @@
         <v>45322</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57401,7 +57401,7 @@
         <v>44974</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>45320</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>45237</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57572,7 +57572,7 @@
         <v>45302</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57629,7 +57629,7 @@
         <v>45715</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>45726</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57743,7 +57743,7 @@
         <v>46059</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57800,7 +57800,7 @@
         <v>45245</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>46064</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57914,7 +57914,7 @@
         <v>46064</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>46066</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>44959</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>44959</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45245</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>46066</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>45313</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>45503</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>45986</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45217</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>44480</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58546,7 +58546,7 @@
         <v>45266</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>44826</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58660,7 +58660,7 @@
         <v>45044</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58717,7 +58717,7 @@
         <v>45235</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         <v>45180</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>45511</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45755</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45040</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45742</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>44883</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59116,7 +59116,7 @@
         <v>45077</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59173,7 +59173,7 @@
         <v>45078</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>46073</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45455</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59344,7 +59344,7 @@
         <v>45299</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59401,7 +59401,7 @@
         <v>45973</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>44882</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>44970</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>45726</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45215</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59691,7 +59691,7 @@
         <v>45485</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59748,7 +59748,7 @@
         <v>45246</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>46013</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>44830</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45978</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59981,7 +59981,7 @@
         <v>45978</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60038,7 +60038,7 @@
         <v>45547</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60095,7 +60095,7 @@
         <v>45463</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>44475</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60209,7 +60209,7 @@
         <v>46085</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60266,7 +60266,7 @@
         <v>46085</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60323,7 +60323,7 @@
         <v>45646</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60380,7 +60380,7 @@
         <v>45470</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>44900</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60494,7 +60494,7 @@
         <v>45679</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60551,7 +60551,7 @@
         <v>45391</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60613,7 +60613,7 @@
         <v>46093</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>44805</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>44565</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60784,7 +60784,7 @@
         <v>46093</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60841,7 +60841,7 @@
         <v>44949</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60898,7 +60898,7 @@
         <v>45184</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60955,7 +60955,7 @@
         <v>44897</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61012,7 +61012,7 @@
         <v>44974</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>44599</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61126,7 +61126,7 @@
         <v>44967</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61183,7 +61183,7 @@
         <v>46095</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61240,7 +61240,7 @@
         <v>46093</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>44606</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>46099</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61411,7 +61411,7 @@
         <v>46098</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61468,7 +61468,7 @@
         <v>46098</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61525,7 +61525,7 @@
         <v>46098</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61582,7 +61582,7 @@
         <v>46098</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61639,7 +61639,7 @@
         <v>46100</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46100</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61753,7 +61753,7 @@
         <v>46100</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>46100</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61867,7 +61867,7 @@
         <v>46100</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61924,7 +61924,7 @@
         <v>46104</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>46104</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         <v>46107</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62100,7 +62100,7 @@
         <v>46107</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62162,7 +62162,7 @@
         <v>46108</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>46112</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>46112</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62333,7 +62333,7 @@
         <v>46161</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46121</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62447,7 +62447,7 @@
         <v>46121</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62504,7 +62504,7 @@
         <v>46162</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62561,7 +62561,7 @@
         <v>46162</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45510</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62675,7 +62675,7 @@
         <v>46162</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62732,7 +62732,7 @@
         <v>46162</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62789,7 +62789,7 @@
         <v>46162</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>46162</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62903,7 +62903,7 @@
         <v>46162</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62960,7 +62960,7 @@
         <v>46162</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63017,7 +63017,7 @@
         <v>46162</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63074,7 +63074,7 @@
         <v>46162</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63131,7 +63131,7 @@
         <v>46124</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>46126</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63245,7 +63245,7 @@
         <v>46168</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63302,7 +63302,7 @@
         <v>46126</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63359,7 +63359,7 @@
         <v>46127</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63416,7 +63416,7 @@
         <v>46104</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>46174</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63530,7 +63530,7 @@
         <v>46007</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63587,7 +63587,7 @@
         <v>46132</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>46129</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63701,7 +63701,7 @@
         <v>46134</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63758,7 +63758,7 @@
         <v>46133</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63815,7 +63815,7 @@
         <v>46175</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63872,7 +63872,7 @@
         <v>46175</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>46175</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63986,7 +63986,7 @@
         <v>46175</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64043,7 +64043,7 @@
         <v>46176</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45670</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64157,7 +64157,7 @@
         <v>45798</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64214,7 +64214,7 @@
         <v>45966</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>46177</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64328,7 +64328,7 @@
         <v>45777</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64385,7 +64385,7 @@
         <v>45736</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64442,7 +64442,7 @@
         <v>44396</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -64499,7 +64499,7 @@
         <v>46176</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -64556,7 +64556,7 @@
         <v>46176</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -64613,7 +64613,7 @@
         <v>44937</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -64670,7 +64670,7 @@
         <v>45789</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         <v>45697</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -64784,7 +64784,7 @@
         <v>44607</v>
       </c>
       <c r="C1082" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1082" t="inlineStr">
         <is>
@@ -64846,7 +64846,7 @@
         <v>44722</v>
       </c>
       <c r="C1083" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1083" t="inlineStr">
         <is>
@@ -64908,7 +64908,7 @@
         <v>44405</v>
       </c>
       <c r="C1084" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1084" t="inlineStr">
         <is>
@@ -64965,7 +64965,7 @@
         <v>46181</v>
       </c>
       <c r="C1085" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1085" t="inlineStr">
         <is>
@@ -65022,7 +65022,7 @@
         <v>46177</v>
       </c>
       <c r="C1086" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1086" t="inlineStr">
         <is>
@@ -65079,7 +65079,7 @@
         <v>45735</v>
       </c>
       <c r="C1087" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1087" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>45266</v>
       </c>
       <c r="C1088" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1088" t="inlineStr">
         <is>
@@ -65193,7 +65193,7 @@
         <v>45260</v>
       </c>
       <c r="C1089" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1089" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>45192</v>
       </c>
       <c r="C1090" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1090" t="inlineStr">
         <is>
@@ -65307,7 +65307,7 @@
         <v>46181</v>
       </c>
       <c r="C1091" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1091" t="inlineStr">
         <is>
@@ -65364,7 +65364,7 @@
         <v>46139</v>
       </c>
       <c r="C1092" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1092" t="inlineStr">
         <is>
@@ -65421,7 +65421,7 @@
         <v>45735</v>
       </c>
       <c r="C1093" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1093" t="inlineStr">
         <is>
@@ -65478,7 +65478,7 @@
         <v>45842</v>
       </c>
       <c r="C1094" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1094" t="inlineStr">
         <is>
@@ -65535,7 +65535,7 @@
         <v>46182</v>
       </c>
       <c r="C1095" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1095" t="inlineStr">
         <is>
@@ -65597,7 +65597,7 @@
         <v>46181</v>
       </c>
       <c r="C1096" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1096" t="inlineStr">
         <is>
@@ -65654,7 +65654,7 @@
         <v>45715</v>
       </c>
       <c r="C1097" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1097" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>46139</v>
       </c>
       <c r="C1098" s="1" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="D1098" t="inlineStr">
         <is>

--- a/Översikt HÄSSLEHOLM.xlsx
+++ b/Översikt HÄSSLEHOLM.xlsx
@@ -566,7 +566,7 @@
         <v>45427</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>45427</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>45427</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>46174</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44378</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45427</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45392</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45348</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>46149</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44952</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>44454</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45687</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45687</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>46168</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45391</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45708</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45812</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45194</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45014</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45687</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45708</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44434</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45463</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44897</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45014</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44862</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45708</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45583</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>46149</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>44809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44659</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44584</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44648</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45714</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45021</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44838</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45378</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45708</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44565</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44896</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45062</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45774</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45617</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45141</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>45817</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45105</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>45825</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45687</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45455</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45648</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45751</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>45750</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45150</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45958</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45341</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45645</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45673</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45266</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45463</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44910</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45566</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45980</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45799</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46013</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45810</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>46098</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>46181</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>46196</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45751</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44883</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44454</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44470</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44886</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>44886</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44438</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44797</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44742</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44454</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44501</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44389</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44406</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>44560</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44799</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44564</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44470</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44454</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44606</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>44652</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44722</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44558</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44456</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44376</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44480</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44488</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44480</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44439</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>44609</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44587</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44887</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44459</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44531</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44735</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44820</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44879</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>44438</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>44438</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44580</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>44806</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44497</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44497</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44796</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44806</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44887</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44480</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44435</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44382</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44846</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>44466</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44616</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44580</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44558</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44463</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>44530</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44844</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44659</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>44433</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44482</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>44461</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44466</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44509</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>44595</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44425</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44397</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44467</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44379</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44375</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44582</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44593</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44565</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44378</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44375</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>44382</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44664</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44588</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44420</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>44735</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44462</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44732</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>44551</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44817</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>44446</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>44581</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44744</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44600</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>44462</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>44511</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44844</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44565</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44441</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>44734</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44606</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44700</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44607</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44999</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45086</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44606</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44462</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44564</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44599</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45702</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45702</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45078</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45632</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44882</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44883</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44875</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44600</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45742</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45751</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45558</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45078</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45078</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44802</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44573</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45561</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45237</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45148</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45462</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45350</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45190</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45702</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45702</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45503</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45320</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45079</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45445</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45005</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45005</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45132</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45132</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>44583</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45471</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45369</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>44533</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44405</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45063</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>44583</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>44959</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44959</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45142</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45617</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45001</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45153</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45259</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45058</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45252</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45191</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44974</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44986</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44986</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>44895</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45057</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45294</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45142</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45313</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44967</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44512</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>44859</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45145</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44820</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45602</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45735</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45247</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44918</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45379</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>44959</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45210</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44937</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44714</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>44515</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45212</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45231</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45667</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45510</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45282</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45254</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45511</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45589</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44944</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45698</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45356</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45356</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45356</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44914</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44452</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>44833</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45510</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45016</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45142</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45254</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45310</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45055</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45517</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45635</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44746</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45726</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45589</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>44916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45547</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44914</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>44375</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44428</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45237</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45001</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45210</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45313</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45087</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45365</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45302</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45202</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45636</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45407</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45321</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45061</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44607</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44881</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44729</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45014</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45245</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45715</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45749</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45620</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45645</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45393</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45168</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45145</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45054</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45715</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45040</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44760</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44858</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44873</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45015</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44949</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45138</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44480</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45191</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45265</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44587</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45323</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45370</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45370</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44847</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45233</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45341</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45043</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>44378</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45470</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45015</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45503</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45233</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44992</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45210</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44438</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44811</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45119</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45353</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44452</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45477</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45750</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45205</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44474</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45302</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45516</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44882</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45629</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44872</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45715</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45253</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44882</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45215</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45560</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45154</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45585</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45463</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45356</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44970</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45569</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45511</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44986</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45518</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45148</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45254</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44805</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45092</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44873</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45447</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45086</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45051</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45461</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45398</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>45040</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44914</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45043</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>44910</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44728</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45322</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45051</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44875</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44910</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45265</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44900</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44949</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45463</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44466</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45391</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45401</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45243</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45180</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45636</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45058</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45723</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44967</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44967</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45726</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45485</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45098</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44599</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45462</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44978</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45688</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45384</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45099</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44981</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45078</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45231</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44992</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44826</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45702</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44958</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45180</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45062</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45617</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45044</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45485</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45109</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44860</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45335</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45446</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45247</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44895</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44802</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45065</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44971</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45084</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44900</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45222</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45077</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45595</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>44454</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>44942</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44719</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44719</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>44963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45734</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>45624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45124</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45646</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45174</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>45156</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45147</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45245</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>44946</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>44946</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44877</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45476</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45119</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45540</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45540</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>45217</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>44897</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45516</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>44831</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45455</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45455</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>44915</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45209</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45209</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45626</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45702</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45594</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44441</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44634</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>44481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44971</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45462</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45006</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>44480</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>44812</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45547</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>44917</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45735</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45646</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45321</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>44897</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45418</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45418</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>44897</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45009</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44974</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>44974</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44599</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45732</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45755</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45463</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45754</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45322</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45322</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45679</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45716</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45107</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45119</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45702</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45447</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45055</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44593</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45576</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>44915</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44953</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45215</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45000</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45184</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45603</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45323</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>45015</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44650</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44957</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44957</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44967</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44792</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45588</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44844</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45147</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45600</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45314</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44739</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45471</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45595</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44882</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44881</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45235</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45399</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44984</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45355</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45462</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45387</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45328</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45217</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45567</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45537</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>44470</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45714</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45050</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45084</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45604</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45456</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44952</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44974</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45503</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>44593</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45204</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45545</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45026</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45114</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>45077</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45812</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45299</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45510</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45117</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45751</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45266</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45715</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45621</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45550</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45096</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>44714</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>45139</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45817</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44820</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45208</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45727</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45016</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44955</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44859</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45219</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>44638</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45821</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45313</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44914</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45821</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44964</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>44950</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>44743</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45435</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>44659</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>44434</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45576</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45217</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45029</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45176</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>44425</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45414</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45532</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>44501</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>44525</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>44940</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45079</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45079</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45510</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45302</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45644</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45092</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44403</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45630</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45063</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45063</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44671</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44671</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44915</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44922</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45524</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45057</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45327</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>45198</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45198</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45832</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45119</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45548</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45224</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45427</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45558</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45558</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45595</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44984</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45314</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>44830</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45626</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44847</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45313</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>44806</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>44742</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45838</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45838</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45478</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45727</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>44981</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44531</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45519</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45303</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45700</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44881</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45702</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45722</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45842</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45096</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45842</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45125</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45844</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44565</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45246</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45844</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45842</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45306</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45695</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45008</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44946</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45849</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>44881</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44379</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44565</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45564</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45756</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45320</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45524</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45210</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44915</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>44915</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45250</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45020</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45777</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45246</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45757</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44998</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45266</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45519</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45092</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45329</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44992</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45161</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45471</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44518</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45754</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45504</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45235</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44868</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45770</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45867</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45077</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45435</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>44475</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45636</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>44775</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>45325</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45321</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44873</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>44746</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>45593</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45023</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>44999</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45708</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>44915</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44615</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45044</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44964</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45124</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45300</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45314</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45485</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45109</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44379</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45876</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>44937</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>44953</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45714</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45839</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45761</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45779</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44490</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45777</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45660</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45469</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45469</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45164</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45644</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45349</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45386</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45485</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45670</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45614</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45646</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45051</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>45313</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45933</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45646</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>44949</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45784</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>45601</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45294</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>45772</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45329</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45727</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45086</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45086</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45245</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45737</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45889</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45628</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45594</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45485</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45799</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>44883</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>45940</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45708</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45891</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45322</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45717</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45105</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45645</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45671</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47526,7 +47526,7 @@
         <v>45747</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>45799</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45946</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45447</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45947</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45105</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45266</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45474</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45600</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45701</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45693</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45720</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45518</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45901</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45901</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>45951</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45774</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45254</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45254</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>44475</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>45789</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45687</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45440</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45905</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>44999</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45790</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>44844</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45755</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45411</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45475</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45503</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45541</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45190</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45008</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45008</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45911</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44972</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>44449</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>45910</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45959</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>44959</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45957</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>45385</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45218</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>44638</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>45554</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45912</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>44553</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45399</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>45912</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45726</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45331</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45675</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45712</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>44810</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45218</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45790</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45644</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45624</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>44981</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51085,7 +51085,7 @@
         <v>45912</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>44883</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>45736</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45190</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45071</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45917</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51427,7 +51427,7 @@
         <v>45917</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45224</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>45929</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45706</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45078</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45919</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>44985</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45044</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45363</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>45734</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45644</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52111,7 +52111,7 @@
         <v>45922</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45692</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52225,7 +52225,7 @@
         <v>44441</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>45923</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>45692</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45362</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45923</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45922</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>44986</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>44986</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45968</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
         <v>45716</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45971</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>45716</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>45796</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>45971</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45926</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45971</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45929</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45926</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45975</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45978</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45978</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45797</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45796</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45796</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45803</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45978</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45622</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>45516</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>45971</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45981</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45513</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45826</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45826</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45721</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>45798</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>45715</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45294</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>45484</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45727</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45475</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>44573</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>45670</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54696,7 +54696,7 @@
         <v>44467</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>45222</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>45800</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>45726</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45800</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45726</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45805</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45805</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55152,7 +55152,7 @@
         <v>46006</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>45812</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55266,7 +55266,7 @@
         <v>46013</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>46013</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>46010</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45351</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>46030</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>46034</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>46034</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>46034</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>46034</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>46035</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>46035</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>46043</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>46043</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>46043</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>46049</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46049</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>46049</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46050</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>46051</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>46055</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>46055</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>46055</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>46057</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>46055</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>46058</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46059</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>46064</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         <v>46066</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56882,7 +56882,7 @@
         <v>46066</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>45986</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45511</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>46073</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45973</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>46085</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57224,7 +57224,7 @@
         <v>46085</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57281,7 +57281,7 @@
         <v>45978</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45978</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46093</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>46098</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>46095</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>46100</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>46100</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>46099</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>46100</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46100</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>46100</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>46104</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57965,7 +57965,7 @@
         <v>46104</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>46107</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>46108</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>46107</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46112</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>46112</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>46162</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>46162</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>46162</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>46162</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>46161</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>46162</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58659,7 +58659,7 @@
         <v>46162</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>46162</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>46162</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>46162</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58887,7 +58887,7 @@
         <v>46162</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>45510</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>46121</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59058,7 +59058,7 @@
         <v>46121</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>46126</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>46124</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46126</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>46168</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>46127</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>46104</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>46175</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>46174</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59571,7 +59571,7 @@
         <v>46133</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>46175</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>46129</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>46175</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>46175</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>46132</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59913,7 +59913,7 @@
         <v>46176</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>46176</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>46176</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>46134</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>45697</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60198,7 +60198,7 @@
         <v>44722</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60260,7 +60260,7 @@
         <v>46139</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>46139</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44396</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>44937</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>44607</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60550,7 +60550,7 @@
         <v>45708</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>44405</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>46181</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>45798</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60778,7 +60778,7 @@
         <v>45260</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45735</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60892,7 +60892,7 @@
         <v>45715</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60949,7 +60949,7 @@
         <v>45966</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61006,7 +61006,7 @@
         <v>45266</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61063,7 +61063,7 @@
         <v>45736</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45735</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>45192</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>46177</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45736</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>45842</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>45789</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>46177</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>45670</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>45777</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>46181</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>46183</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>46182</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45008</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>46050</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>46182</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>46182</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
         <v>46182</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62094,7 +62094,7 @@
         <v>46182</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
         <v>46181</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62208,7 +62208,7 @@
         <v>46182</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>46183</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62322,7 +62322,7 @@
         <v>46182</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>46162</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45930</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>45930</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>45930</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45930</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>46188</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45930</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62778,7 +62778,7 @@
         <v>46188</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>45966</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>46188</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>46132</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
         <v>46135</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>46149</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46149</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>46149</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63234,7 +63234,7 @@
         <v>46149</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63291,7 +63291,7 @@
         <v>46148</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63348,7 +63348,7 @@
         <v>46149</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63405,7 +63405,7 @@
         <v>46149</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63462,7 +63462,7 @@
         <v>46195</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45348</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>46192</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63633,7 +63633,7 @@
         <v>46007</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63690,7 +63690,7 @@
         <v>45636</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>44588</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63804,7 +63804,7 @@
         <v>46196</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63861,7 +63861,7 @@
         <v>45645</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>45817</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>46198</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>46199</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64089,7 +64089,7 @@
         <v>45965</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64146,7 +64146,7 @@
         <v>46199</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>46198</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>46055</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>46198</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>46174</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>45335</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>

--- a/Översikt HÄSSLEHOLM.xlsx
+++ b/Översikt HÄSSLEHOLM.xlsx
@@ -566,7 +566,7 @@
         <v>45427</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
         <v>45427</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>45427</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>46174</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44378</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>45427</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>45392</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>45348</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>46149</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44952</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>44454</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45687</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45687</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>46168</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>45391</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45708</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>45812</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45194</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45014</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>45687</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45708</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>44434</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>45463</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>44897</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>45014</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>44862</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>45708</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45583</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>46149</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>44809</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44659</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>44584</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44648</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45714</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45021</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>44838</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45378</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>45708</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>44565</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44896</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45062</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>45774</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>45617</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45141</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
         <v>45817</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>45105</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>45825</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         <v>45687</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45455</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45648</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45751</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>45750</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>45385</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>45150</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45958</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>45341</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>45645</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>45673</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>45266</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>45463</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44910</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>45566</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>45980</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>45799</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>46013</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45810</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>46098</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>46181</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>46196</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>45751</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44883</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44454</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44470</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44886</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
         <v>44886</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44438</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>44797</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44742</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>44454</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44501</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44389</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>44406</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>44560</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44799</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>44564</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         <v>44470</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>44454</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>44606</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         <v>44652</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>44722</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44558</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44456</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44376</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44480</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44488</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44488</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44480</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         <v>44439</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>44609</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44452</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44587</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44887</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44459</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>44531</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44735</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>44820</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>44879</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>44438</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>44438</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44580</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>44806</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>44497</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44497</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44796</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>44806</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>44887</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>44480</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>44435</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>44382</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>44558</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44846</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         <v>44466</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44616</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>44580</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>44584</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44558</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>44463</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>44530</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>44844</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44659</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>44433</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         <v>44482</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>44461</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>44466</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44509</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>44595</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>44425</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44397</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>44467</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44379</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44375</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44582</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44593</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44565</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44378</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44495</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44375</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>44382</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>44664</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44588</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>44573</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>44420</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>44735</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44462</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44732</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>44551</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44817</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>44446</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11976,7 +11976,7 @@
         <v>44581</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>44744</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>44600</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>44462</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44887</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>44511</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>44844</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12380,7 +12380,7 @@
         <v>44565</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44441</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>44734</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>44606</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44700</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44607</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44999</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45086</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12846,7 +12846,7 @@
         <v>44606</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>44462</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>44564</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>44599</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45702</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>45702</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45078</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45632</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>44882</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>44883</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>44875</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>44600</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45742</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>45742</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45751</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45558</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>45078</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45078</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>44802</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44573</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45561</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45237</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45148</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45462</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45350</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>45190</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>45702</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45702</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45503</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
         <v>45320</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45079</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>45445</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>45005</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>45005</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45132</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45132</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>44583</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45471</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45369</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>44533</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44405</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45063</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>44583</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>44959</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>44959</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45142</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45617</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45001</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45153</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45259</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45058</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45252</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45191</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>44974</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>45125</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44986</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>44986</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>44895</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45057</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45294</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>45142</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45313</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44967</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>44512</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>44859</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45145</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>44820</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45602</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45735</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>45247</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>44918</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45379</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>44959</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17228,7 +17228,7 @@
         <v>45210</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17285,7 +17285,7 @@
         <v>44937</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44714</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>44515</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45212</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45231</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17570,7 +17570,7 @@
         <v>45667</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45510</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
         <v>45444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45282</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45254</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45511</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45589</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44944</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>45698</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18088,7 +18088,7 @@
         <v>45356</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45356</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45356</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44914</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44452</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>44833</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45510</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45016</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45142</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45254</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18658,7 +18658,7 @@
         <v>45310</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45055</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>45517</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45635</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18886,7 +18886,7 @@
         <v>44746</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45726</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45589</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>44916</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45547</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44914</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>44375</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>44428</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19342,7 +19342,7 @@
         <v>45237</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>45001</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45210</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45313</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45087</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45365</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45302</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19741,7 +19741,7 @@
         <v>45202</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45636</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45407</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45321</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45061</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>44607</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44881</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44729</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45014</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45245</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45715</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45749</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45620</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45645</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45393</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45168</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45145</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45054</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>44977</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45715</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45040</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44760</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44858</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44873</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45015</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44949</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45138</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>44480</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45191</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45148</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45265</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44463</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>44587</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45323</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>45370</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45370</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>45519</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>44847</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45233</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45341</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>45043</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>44378</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45470</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45015</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45503</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45233</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44992</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45210</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44438</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44811</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45119</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45353</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44452</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45477</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45750</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22958,7 +22958,7 @@
         <v>45205</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>44474</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45222</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>44448</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45302</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45516</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44882</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45629</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>44872</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45715</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45253</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>44882</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45215</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45560</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45154</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>45585</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45463</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45356</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>44970</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45569</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45511</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44986</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45518</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45148</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45254</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>44805</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>45092</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44873</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>45447</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45086</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45051</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>45461</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45398</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>45040</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>44914</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45043</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>44910</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>44728</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>45322</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45051</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44875</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>44910</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45265</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>44900</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>44949</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25605,7 +25605,7 @@
         <v>45463</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44466</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45391</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45401</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>45243</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45180</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>45636</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26009,7 +26009,7 @@
         <v>45058</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45723</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44967</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>44967</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45726</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45485</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45098</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>44599</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>45462</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44978</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45688</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>45384</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>45099</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>44981</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45078</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45231</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>44992</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26983,7 +26983,7 @@
         <v>44826</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27040,7 +27040,7 @@
         <v>45702</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>44958</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45180</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>45062</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45617</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27330,7 +27330,7 @@
         <v>45044</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27387,7 +27387,7 @@
         <v>45485</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45109</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>44860</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45335</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45446</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45247</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44895</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>44802</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45065</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45348</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>44971</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45084</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>44900</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45222</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45077</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45595</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28299,7 +28299,7 @@
         <v>44454</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>44942</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>44719</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44719</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28542,7 +28542,7 @@
         <v>44963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45734</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>45624</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45124</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45646</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45174</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>45156</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45147</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45245</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>44946</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>44946</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29174,7 +29174,7 @@
         <v>44877</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         <v>45476</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45119</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>45540</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45540</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>45217</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>44897</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45516</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>44831</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45455</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>45455</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>44915</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>45209</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29920,7 +29920,7 @@
         <v>45209</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45626</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45702</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45594</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>44441</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>44634</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30262,7 +30262,7 @@
         <v>44481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>44971</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>45462</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30433,7 +30433,7 @@
         <v>45006</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>44480</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>44812</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45547</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>44917</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>45735</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30780,7 +30780,7 @@
         <v>45646</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45321</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>44897</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45418</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45418</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31065,7 +31065,7 @@
         <v>44897</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31122,7 +31122,7 @@
         <v>45009</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31179,7 +31179,7 @@
         <v>44974</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>44974</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44599</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>45732</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45755</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45463</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45754</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31578,7 +31578,7 @@
         <v>45322</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45322</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45679</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
         <v>45716</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31806,7 +31806,7 @@
         <v>45107</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31863,7 +31863,7 @@
         <v>45119</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31920,7 +31920,7 @@
         <v>45702</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>45447</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32034,7 +32034,7 @@
         <v>45055</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>44593</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45576</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>44915</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>44953</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>45215</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45000</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>45184</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45603</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32547,7 +32547,7 @@
         <v>45323</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32604,7 +32604,7 @@
         <v>45015</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>44650</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>44957</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>44957</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44967</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44792</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>45588</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44844</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45147</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33117,7 +33117,7 @@
         <v>45600</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45314</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>44739</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45471</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33350,7 +33350,7 @@
         <v>45595</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33407,7 +33407,7 @@
         <v>44882</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33464,7 +33464,7 @@
         <v>44881</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>44812</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>45235</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45399</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33692,7 +33692,7 @@
         <v>44984</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>45355</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33806,7 +33806,7 @@
         <v>45462</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45387</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33920,7 +33920,7 @@
         <v>45328</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33977,7 +33977,7 @@
         <v>45217</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45567</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45537</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34148,7 +34148,7 @@
         <v>44470</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>45714</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45050</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45084</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>45604</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34433,7 +34433,7 @@
         <v>45456</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34490,7 +34490,7 @@
         <v>44952</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44974</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45503</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34661,7 +34661,7 @@
         <v>44593</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34718,7 +34718,7 @@
         <v>45204</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45545</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>45026</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45114</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34946,7 +34946,7 @@
         <v>45077</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35003,7 +35003,7 @@
         <v>45812</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>45299</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45510</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>45117</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45751</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45266</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45715</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45621</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35459,7 +35459,7 @@
         <v>45550</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>45096</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>44714</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>45139</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35687,7 +35687,7 @@
         <v>45817</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45817</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45817</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35858,7 +35858,7 @@
         <v>44820</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45208</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>45727</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>45016</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36086,7 +36086,7 @@
         <v>45665</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>44955</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36200,7 +36200,7 @@
         <v>44859</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45219</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36319,7 +36319,7 @@
         <v>44638</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45821</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>45313</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>44914</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45821</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>44964</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>44950</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>44743</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36775,7 +36775,7 @@
         <v>45435</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36832,7 +36832,7 @@
         <v>44659</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>44434</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45576</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37008,7 +37008,7 @@
         <v>45217</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37065,7 +37065,7 @@
         <v>45029</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37122,7 +37122,7 @@
         <v>45176</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>44425</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37236,7 +37236,7 @@
         <v>45414</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37293,7 +37293,7 @@
         <v>45532</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>44501</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>44525</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>44940</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45079</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45079</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45510</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45302</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45644</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45092</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44403</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45092</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45630</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         <v>45063</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>45063</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44671</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44671</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>44915</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44922</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45524</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>45057</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45327</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38614,7 +38614,7 @@
         <v>45198</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>45198</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38728,7 +38728,7 @@
         <v>45832</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>45119</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>44918</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38899,7 +38899,7 @@
         <v>45548</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38956,7 +38956,7 @@
         <v>45224</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45427</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45558</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45558</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45595</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44984</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45314</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39355,7 +39355,7 @@
         <v>44830</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39412,7 +39412,7 @@
         <v>45626</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>44847</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45313</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39583,7 +39583,7 @@
         <v>44806</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>44742</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>45838</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>45838</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>44963</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45478</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45727</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>44981</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44531</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44951</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45519</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45303</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45700</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44881</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45702</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45722</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>45842</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45096</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45842</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>45125</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45844</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44565</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45246</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>45844</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>45842</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>45306</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45695</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41122,7 +41122,7 @@
         <v>45008</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>44946</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41236,7 +41236,7 @@
         <v>45849</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>44881</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41350,7 +41350,7 @@
         <v>44379</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41407,7 +41407,7 @@
         <v>44565</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41464,7 +41464,7 @@
         <v>45564</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41521,7 +41521,7 @@
         <v>45756</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41578,7 +41578,7 @@
         <v>45320</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41635,7 +41635,7 @@
         <v>45524</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45210</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41749,7 +41749,7 @@
         <v>44915</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41806,7 +41806,7 @@
         <v>44915</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>45250</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45020</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45777</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45246</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45757</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42262,7 +42262,7 @@
         <v>44998</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45266</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45519</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45092</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>45329</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>44992</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45161</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42666,7 +42666,7 @@
         <v>45471</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42723,7 +42723,7 @@
         <v>44518</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42780,7 +42780,7 @@
         <v>45754</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>45504</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42894,7 +42894,7 @@
         <v>45235</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44868</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45770</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45867</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45077</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45435</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>44475</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45636</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>44775</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45593</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43469,7 +43469,7 @@
         <v>45325</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>45321</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43583,7 +43583,7 @@
         <v>44873</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43640,7 +43640,7 @@
         <v>44746</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43697,7 +43697,7 @@
         <v>45593</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45023</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>44999</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45708</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>44915</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44615</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45044</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>44964</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45124</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45300</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>45314</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45485</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45109</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44379</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45876</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>44937</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>44953</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>44830</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45714</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45839</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45761</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45779</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44956,7 +44956,7 @@
         <v>44490</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45013,7 +45013,7 @@
         <v>45777</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45070,7 +45070,7 @@
         <v>45660</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45127,7 +45127,7 @@
         <v>45469</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45469</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45164</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45644</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45349</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45386</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45485</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45526,7 +45526,7 @@
         <v>45670</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45583,7 +45583,7 @@
         <v>45614</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45640,7 +45640,7 @@
         <v>45646</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45697,7 +45697,7 @@
         <v>45051</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>45313</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45811,7 +45811,7 @@
         <v>45933</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45868,7 +45868,7 @@
         <v>45646</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>44949</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45784</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46039,7 +46039,7 @@
         <v>45601</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46096,7 +46096,7 @@
         <v>45294</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46153,7 +46153,7 @@
         <v>45772</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>45329</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45727</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45086</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45086</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45245</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>44937</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>45737</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>45889</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45628</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45594</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>45485</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46837,7 +46837,7 @@
         <v>45799</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46894,7 +46894,7 @@
         <v>45889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46951,7 +46951,7 @@
         <v>44883</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>45940</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45708</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45891</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45322</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45717</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47298,7 +47298,7 @@
         <v>45105</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>45645</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47412,7 +47412,7 @@
         <v>45555</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45671</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47526,7 +47526,7 @@
         <v>45747</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>45799</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45946</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45447</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45947</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45243</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45105</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45266</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45474</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45600</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45701</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45693</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45720</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45518</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45209</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45901</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45901</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>45951</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45774</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45254</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45254</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>44475</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>45789</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48837,7 +48837,7 @@
         <v>45687</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48894,7 +48894,7 @@
         <v>45440</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>45905</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49008,7 +49008,7 @@
         <v>44999</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45790</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49122,7 +49122,7 @@
         <v>44844</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>45755</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45411</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45475</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45503</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45541</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45190</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45008</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45008</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45911</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>44972</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>44449</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>45910</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>45959</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49930,7 +49930,7 @@
         <v>44959</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49987,7 +49987,7 @@
         <v>45957</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -50044,7 +50044,7 @@
         <v>45385</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -50101,7 +50101,7 @@
         <v>45218</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>44638</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>45554</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45912</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>44553</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50386,7 +50386,7 @@
         <v>45399</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50443,7 +50443,7 @@
         <v>45912</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50500,7 +50500,7 @@
         <v>45726</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>45331</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         <v>45675</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50676,7 +50676,7 @@
         <v>45712</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50733,7 +50733,7 @@
         <v>44810</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45218</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45790</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45644</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45624</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -51028,7 +51028,7 @@
         <v>44981</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -51085,7 +51085,7 @@
         <v>45912</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -51142,7 +51142,7 @@
         <v>44883</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51199,7 +51199,7 @@
         <v>45736</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51256,7 +51256,7 @@
         <v>45190</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45071</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45917</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51427,7 +51427,7 @@
         <v>45917</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51484,7 +51484,7 @@
         <v>45224</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>45929</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45706</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51655,7 +51655,7 @@
         <v>45078</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45919</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>44985</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45217</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51883,7 +51883,7 @@
         <v>45044</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         <v>45363</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51997,7 +51997,7 @@
         <v>45734</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45644</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -52111,7 +52111,7 @@
         <v>45922</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45692</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52225,7 +52225,7 @@
         <v>44441</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52282,7 +52282,7 @@
         <v>45923</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>45692</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -52396,7 +52396,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -52453,7 +52453,7 @@
         <v>45362</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45923</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -52567,7 +52567,7 @@
         <v>45922</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -52624,7 +52624,7 @@
         <v>44986</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>44986</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -52748,7 +52748,7 @@
         <v>45968</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -52805,7 +52805,7 @@
         <v>45716</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -52862,7 +52862,7 @@
         <v>45971</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -52919,7 +52919,7 @@
         <v>45716</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>45796</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -53033,7 +53033,7 @@
         <v>45971</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45926</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -53147,7 +53147,7 @@
         <v>45971</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>45929</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -53261,7 +53261,7 @@
         <v>45926</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45975</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45978</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45978</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45797</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45796</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45796</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45803</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45978</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45622</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>45516</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -53888,7 +53888,7 @@
         <v>45971</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -53945,7 +53945,7 @@
         <v>45981</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -54002,7 +54002,7 @@
         <v>45513</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -54059,7 +54059,7 @@
         <v>45826</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -54116,7 +54116,7 @@
         <v>45826</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45721</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -54230,7 +54230,7 @@
         <v>45798</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>45715</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>45294</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -54401,7 +54401,7 @@
         <v>45484</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -54458,7 +54458,7 @@
         <v>45727</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -54515,7 +54515,7 @@
         <v>45475</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>44573</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -54639,7 +54639,7 @@
         <v>45670</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -54696,7 +54696,7 @@
         <v>44467</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -54753,7 +54753,7 @@
         <v>45222</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -54810,7 +54810,7 @@
         <v>45800</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>45726</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>45800</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -54981,7 +54981,7 @@
         <v>45726</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>45805</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45805</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -55152,7 +55152,7 @@
         <v>46006</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -55209,7 +55209,7 @@
         <v>45812</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -55266,7 +55266,7 @@
         <v>46013</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -55323,7 +55323,7 @@
         <v>46013</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -55385,7 +55385,7 @@
         <v>46010</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45351</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>46030</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         <v>46034</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>46034</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -55675,7 +55675,7 @@
         <v>46034</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -55732,7 +55732,7 @@
         <v>46034</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -55789,7 +55789,7 @@
         <v>46035</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>46035</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -55913,7 +55913,7 @@
         <v>46043</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>46043</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
         <v>46043</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -56084,7 +56084,7 @@
         <v>46049</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46049</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -56198,7 +56198,7 @@
         <v>46049</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
         <v>46050</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -56312,7 +56312,7 @@
         <v>46051</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -56369,7 +56369,7 @@
         <v>46055</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>46055</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -56483,7 +56483,7 @@
         <v>46055</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>46057</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -56597,7 +56597,7 @@
         <v>46055</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>46058</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>46059</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -56768,7 +56768,7 @@
         <v>46064</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -56825,7 +56825,7 @@
         <v>46066</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -56882,7 +56882,7 @@
         <v>46066</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -56939,7 +56939,7 @@
         <v>45986</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>45511</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>46073</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
         <v>45973</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>46085</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -57224,7 +57224,7 @@
         <v>46085</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -57281,7 +57281,7 @@
         <v>45978</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45978</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46093</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>46098</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>46095</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>46100</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>46100</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>46099</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -57737,7 +57737,7 @@
         <v>46100</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>46100</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>46100</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>46104</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -57965,7 +57965,7 @@
         <v>46104</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>46107</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -58084,7 +58084,7 @@
         <v>46108</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -58141,7 +58141,7 @@
         <v>46107</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>46112</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>46112</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>46162</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>46162</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>46162</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>46162</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>46161</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -58602,7 +58602,7 @@
         <v>46162</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -58659,7 +58659,7 @@
         <v>46162</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -58716,7 +58716,7 @@
         <v>46162</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -58773,7 +58773,7 @@
         <v>46162</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>46162</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -58887,7 +58887,7 @@
         <v>46162</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -58944,7 +58944,7 @@
         <v>45510</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>46121</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -59058,7 +59058,7 @@
         <v>46121</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>46126</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -59172,7 +59172,7 @@
         <v>46124</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -59229,7 +59229,7 @@
         <v>46126</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -59286,7 +59286,7 @@
         <v>46168</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -59343,7 +59343,7 @@
         <v>46127</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -59400,7 +59400,7 @@
         <v>46104</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -59457,7 +59457,7 @@
         <v>46175</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>46174</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -59571,7 +59571,7 @@
         <v>46133</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -59628,7 +59628,7 @@
         <v>46175</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -59685,7 +59685,7 @@
         <v>46129</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -59742,7 +59742,7 @@
         <v>46175</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -59799,7 +59799,7 @@
         <v>46175</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>46132</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -59913,7 +59913,7 @@
         <v>46176</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>46176</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -60027,7 +60027,7 @@
         <v>46176</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -60084,7 +60084,7 @@
         <v>46134</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>45697</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -60198,7 +60198,7 @@
         <v>44722</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -60260,7 +60260,7 @@
         <v>46139</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>46139</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -60374,7 +60374,7 @@
         <v>44396</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>44937</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -60488,7 +60488,7 @@
         <v>44607</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -60550,7 +60550,7 @@
         <v>45708</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>44405</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>46181</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -60721,7 +60721,7 @@
         <v>45798</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -60778,7 +60778,7 @@
         <v>45260</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45735</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -60892,7 +60892,7 @@
         <v>45715</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -60949,7 +60949,7 @@
         <v>45966</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -61006,7 +61006,7 @@
         <v>45266</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -61063,7 +61063,7 @@
         <v>45736</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45735</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>45192</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>46177</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -61291,7 +61291,7 @@
         <v>45736</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>45842</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -61405,7 +61405,7 @@
         <v>45789</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>46177</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -61519,7 +61519,7 @@
         <v>45670</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>45777</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>46181</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>46183</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -61747,7 +61747,7 @@
         <v>46182</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45008</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -61861,7 +61861,7 @@
         <v>46050</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -61918,7 +61918,7 @@
         <v>46182</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -61975,7 +61975,7 @@
         <v>46182</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -62037,7 +62037,7 @@
         <v>46182</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -62094,7 +62094,7 @@
         <v>46182</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -62151,7 +62151,7 @@
         <v>46181</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -62208,7 +62208,7 @@
         <v>46182</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>46183</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -62322,7 +62322,7 @@
         <v>46182</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>46162</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45930</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -62493,7 +62493,7 @@
         <v>45930</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -62550,7 +62550,7 @@
         <v>45930</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45930</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>46188</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -62721,7 +62721,7 @@
         <v>45930</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -62778,7 +62778,7 @@
         <v>46188</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -62835,7 +62835,7 @@
         <v>45966</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -62892,7 +62892,7 @@
         <v>46188</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -62949,7 +62949,7 @@
         <v>46132</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -63006,7 +63006,7 @@
         <v>46135</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>46149</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46149</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -63177,7 +63177,7 @@
         <v>46149</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -63234,7 +63234,7 @@
         <v>46149</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -63291,7 +63291,7 @@
         <v>46148</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -63348,7 +63348,7 @@
         <v>46149</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -63405,7 +63405,7 @@
         <v>46149</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -63462,7 +63462,7 @@
         <v>46195</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45348</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -63576,7 +63576,7 @@
         <v>46192</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -63633,7 +63633,7 @@
         <v>46007</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -63690,7 +63690,7 @@
         <v>45636</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>44588</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -63804,7 +63804,7 @@
         <v>46196</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -63861,7 +63861,7 @@
         <v>45645</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>45817</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -63975,7 +63975,7 @@
         <v>46198</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -64032,7 +64032,7 @@
         <v>46199</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -64089,7 +64089,7 @@
         <v>45965</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -64146,7 +64146,7 @@
         <v>46199</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -64203,7 +64203,7 @@
         <v>46198</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>46055</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>46198</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>46174</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -64431,7 +64431,7 @@
         <v>45335</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
